--- a/nr-securitylabel-slicing-123/ig/all-profiles.xlsx
+++ b/nr-securitylabel-slicing-123/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:28:00+00:00</t>
+    <t>2026-08-06T13:33:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -943,7 +943,7 @@
     <t>Use of the Health Care Privacy/Security Classification (HCS) system of security-tag use is recommended.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:$this}
+    <t xml:space="preserve">value:$this}
 </t>
   </si>
   <si>

--- a/nr-securitylabel-slicing-123/ig/all-profiles.xlsx
+++ b/nr-securitylabel-slicing-123/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25067" uniqueCount="1333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25067" uniqueCount="1334">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:55:54+00:00</t>
+    <t>2026-08-06T14:05:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -968,7 +968,7 @@
     <t>visibilityStatus</t>
   </si>
   <si>
-    <t>Statut de visibilité complémentaire du document (motifs de masquage patient, représentants légaux, professionnels).</t>
+    <t>Statut de visibilité du document (invisible patient, invisible représentants légaux, masqué PS, etc...).</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J110-StatutVisibiliteDocument-CISIS/FHIR/JDV-J110-StatutVisibiliteDocument-CISIS</t>
@@ -3918,6 +3918,9 @@
   </si>
   <si>
     <t>Commentaire associé au document.</t>
+  </si>
+  <si>
+    <t>Statut de visibilité complémentaire du document (motifs de masquage patient, représentants légaux, professionnels).</t>
   </si>
   <si>
     <t>Document contenu.</t>
@@ -5654,7 +5657,7 @@
         <v>2</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="174">
@@ -5662,7 +5665,7 @@
         <v>4</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="175">
@@ -5678,7 +5681,7 @@
         <v>8</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="177">
@@ -5686,7 +5689,7 @@
         <v>10</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="178">
@@ -5740,7 +5743,7 @@
         <v>23</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="185">
@@ -5784,7 +5787,7 @@
         <v>33</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="191">
@@ -75123,7 +75126,7 @@
         <v>220</v>
       </c>
       <c r="M664" t="s" s="2">
-        <v>300</v>
+        <v>1252</v>
       </c>
       <c r="N664" t="s" s="2">
         <v>289</v>
@@ -75228,7 +75231,7 @@
         <v>258</v>
       </c>
       <c r="M665" t="s" s="2">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="N665" t="s" s="2">
         <v>304</v>
@@ -76167,7 +76170,7 @@
         <v>329</v>
       </c>
       <c r="M674" t="s" s="2">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="N674" t="s" s="2">
         <v>331</v>
@@ -76274,7 +76277,7 @@
         <v>336</v>
       </c>
       <c r="M675" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="N675" t="s" s="2">
         <v>338</v>
@@ -76700,7 +76703,7 @@
         <v>364</v>
       </c>
       <c r="M679" t="s" s="2">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="N679" t="s" s="2">
         <v>366</v>
@@ -77703,7 +77706,7 @@
         <v>75</v>
       </c>
       <c r="AK688" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="689">
@@ -77808,7 +77811,7 @@
         <v>75</v>
       </c>
       <c r="AK689" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="690">
@@ -78021,7 +78024,7 @@
     </row>
     <row r="692">
       <c r="A692" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B692" t="s" s="2">
         <v>1103</v>
@@ -78124,7 +78127,7 @@
     </row>
     <row r="693">
       <c r="A693" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B693" t="s" s="2">
         <v>1106</v>
@@ -78229,7 +78232,7 @@
     </row>
     <row r="694">
       <c r="A694" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B694" t="s" s="2">
         <v>1107</v>
@@ -78332,7 +78335,7 @@
     </row>
     <row r="695">
       <c r="A695" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B695" t="s" s="2">
         <v>1108</v>
@@ -78435,7 +78438,7 @@
     </row>
     <row r="696">
       <c r="A696" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B696" t="s" s="2">
         <v>1109</v>
@@ -78540,7 +78543,7 @@
     </row>
     <row r="697">
       <c r="A697" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B697" t="s" s="2">
         <v>1110</v>
@@ -78645,7 +78648,7 @@
     </row>
     <row r="698">
       <c r="A698" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B698" t="s" s="2">
         <v>1111</v>
@@ -78750,7 +78753,7 @@
     </row>
     <row r="699">
       <c r="A699" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B699" t="s" s="2">
         <v>1112</v>
@@ -78855,7 +78858,7 @@
     </row>
     <row r="700">
       <c r="A700" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B700" t="s" s="2">
         <v>1113</v>
@@ -78960,7 +78963,7 @@
     </row>
     <row r="701">
       <c r="A701" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B701" t="s" s="2">
         <v>1114</v>
@@ -79065,7 +79068,7 @@
     </row>
     <row r="702">
       <c r="A702" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B702" t="s" s="2">
         <v>1115</v>
@@ -79170,7 +79173,7 @@
     </row>
     <row r="703">
       <c r="A703" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B703" t="s" s="2">
         <v>1116</v>
@@ -79275,7 +79278,7 @@
     </row>
     <row r="704">
       <c r="A704" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B704" t="s" s="2">
         <v>1117</v>
@@ -79380,7 +79383,7 @@
     </row>
     <row r="705">
       <c r="A705" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B705" t="s" s="2">
         <v>1118</v>
@@ -79485,7 +79488,7 @@
     </row>
     <row r="706">
       <c r="A706" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B706" t="s" s="2">
         <v>1119</v>
@@ -79517,7 +79520,7 @@
         <v>176</v>
       </c>
       <c r="M706" t="s" s="2">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="N706" t="s" s="2">
         <v>178</v>
@@ -79590,7 +79593,7 @@
     </row>
     <row r="707">
       <c r="A707" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B707" t="s" s="2">
         <v>1121</v>
@@ -79604,7 +79607,7 @@
       </c>
       <c r="F707" s="2"/>
       <c r="G707" t="s" s="2">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H707" t="s" s="2">
         <v>77</v>
@@ -79691,7 +79694,7 @@
     </row>
     <row r="708">
       <c r="A708" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B708" t="s" s="2">
         <v>1122</v>
@@ -79725,7 +79728,7 @@
         <v>1124</v>
       </c>
       <c r="M708" t="s" s="2">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="N708" t="s" s="2">
         <v>1126</v>
@@ -79791,18 +79794,18 @@
         <v>190</v>
       </c>
       <c r="AK708" t="s" s="2">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B709" t="s" s="2">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="C709" t="s" s="2">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="D709" s="2"/>
       <c r="E709" t="s" s="2">
@@ -79899,13 +79902,13 @@
     </row>
     <row r="710">
       <c r="A710" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B710" t="s" s="2">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="C710" t="s" s="2">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="D710" s="2"/>
       <c r="E710" t="s" s="2">
@@ -80002,13 +80005,13 @@
     </row>
     <row r="711">
       <c r="A711" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B711" t="s" s="2">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="C711" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="D711" s="2"/>
       <c r="E711" t="s" s="2">
@@ -80048,7 +80051,7 @@
       </c>
       <c r="R711" s="2"/>
       <c r="S711" t="s" s="2">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="T711" t="s" s="2">
         <v>75</v>
@@ -80107,13 +80110,13 @@
     </row>
     <row r="712">
       <c r="A712" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B712" t="s" s="2">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="C712" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="D712" s="2"/>
       <c r="E712" t="s" s="2">
@@ -80173,7 +80176,7 @@
       </c>
       <c r="Z712" s="2"/>
       <c r="AA712" t="s" s="2">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="AB712" t="s" s="2">
         <v>75</v>
@@ -80208,16 +80211,16 @@
     </row>
     <row r="713">
       <c r="A713" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B713" t="s" s="2">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="C713" t="s" s="2">
         <v>1121</v>
       </c>
       <c r="D713" t="s" s="2">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="E713" t="s" s="2">
         <v>75</v>
@@ -80239,13 +80242,13 @@
         <v>75</v>
       </c>
       <c r="L713" t="s" s="2">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="M713" t="s" s="2">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="N713" t="s" s="2">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="O713" s="2"/>
       <c r="P713" s="2"/>
@@ -80313,16 +80316,16 @@
     </row>
     <row r="714">
       <c r="A714" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B714" t="s" s="2">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="C714" t="s" s="2">
         <v>1121</v>
       </c>
       <c r="D714" t="s" s="2">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="E714" t="s" s="2">
         <v>75</v>
@@ -80344,13 +80347,13 @@
         <v>75</v>
       </c>
       <c r="L714" t="s" s="2">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="M714" t="s" s="2">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="N714" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="O714" s="2"/>
       <c r="P714" s="2"/>
@@ -80418,10 +80421,10 @@
     </row>
     <row r="715">
       <c r="A715" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B715" t="s" s="2">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C715" t="s" s="2">
         <v>1121</v>
@@ -80452,7 +80455,7 @@
         <v>187</v>
       </c>
       <c r="M715" t="s" s="2">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="N715" t="s" s="2">
         <v>189</v>
@@ -80523,16 +80526,16 @@
     </row>
     <row r="716">
       <c r="A716" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B716" t="s" s="2">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="C716" t="s" s="2">
         <v>1121</v>
       </c>
       <c r="D716" t="s" s="2">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="E716" t="s" s="2">
         <v>75</v>
@@ -80554,10 +80557,10 @@
         <v>75</v>
       </c>
       <c r="L716" t="s" s="2">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="M716" t="s" s="2">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="N716" t="s" s="2">
         <v>998</v>
@@ -80628,13 +80631,13 @@
     </row>
     <row r="717">
       <c r="A717" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B717" t="s" s="2">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="C717" t="s" s="2">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="D717" s="2"/>
       <c r="E717" t="s" s="2">
@@ -80731,13 +80734,13 @@
     </row>
     <row r="718">
       <c r="A718" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B718" t="s" s="2">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="C718" t="s" s="2">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="D718" s="2"/>
       <c r="E718" t="s" s="2">
@@ -80834,13 +80837,13 @@
     </row>
     <row r="719">
       <c r="A719" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B719" t="s" s="2">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="C719" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="D719" s="2"/>
       <c r="E719" t="s" s="2">
@@ -80939,13 +80942,13 @@
     </row>
     <row r="720">
       <c r="A720" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B720" t="s" s="2">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="C720" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="D720" s="2"/>
       <c r="E720" t="s" s="2">
@@ -81042,7 +81045,7 @@
     </row>
     <row r="721">
       <c r="A721" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B721" t="s" s="2">
         <v>1127</v>
@@ -81145,7 +81148,7 @@
     </row>
     <row r="722">
       <c r="A722" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B722" t="s" s="2">
         <v>1128</v>
@@ -81246,7 +81249,7 @@
     </row>
     <row r="723">
       <c r="A723" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B723" t="s" s="2">
         <v>1131</v>
@@ -81277,10 +81280,10 @@
         <v>75</v>
       </c>
       <c r="L723" t="s" s="2">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="M723" t="s" s="2">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="N723" t="s" s="2">
         <v>1130</v>
@@ -81351,7 +81354,7 @@
     </row>
     <row r="724">
       <c r="A724" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B724" t="s" s="2">
         <v>1134</v>
@@ -81385,7 +81388,7 @@
         <v>206</v>
       </c>
       <c r="M724" t="s" s="2">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="N724" t="s" s="2">
         <v>1130</v>
@@ -81456,7 +81459,7 @@
     </row>
     <row r="725">
       <c r="A725" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B725" t="s" s="2">
         <v>1136</v>
@@ -81488,7 +81491,7 @@
         <v>159</v>
       </c>
       <c r="M725" t="s" s="2">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="N725" t="s" s="2">
         <v>1138</v>
@@ -81561,7 +81564,7 @@
     </row>
     <row r="726">
       <c r="A726" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B726" t="s" s="2">
         <v>1142</v>
@@ -81593,7 +81596,7 @@
         <v>159</v>
       </c>
       <c r="M726" t="s" s="2">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="N726" t="s" s="2">
         <v>1144</v>
@@ -81668,7 +81671,7 @@
     </row>
     <row r="727">
       <c r="A727" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B727" t="s" s="2">
         <v>1150</v>
@@ -81700,7 +81703,7 @@
         <v>98</v>
       </c>
       <c r="M727" t="s" s="2">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="N727" t="s" s="2">
         <v>1152</v>
@@ -81773,7 +81776,7 @@
     </row>
     <row r="728">
       <c r="A728" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B728" t="s" s="2">
         <v>1155</v>
@@ -81805,7 +81808,7 @@
         <v>220</v>
       </c>
       <c r="M728" t="s" s="2">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="N728" t="s" s="2">
         <v>1157</v>
@@ -81824,7 +81827,7 @@
         <v>75</v>
       </c>
       <c r="T728" t="s" s="2">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="U728" t="s" s="2">
         <v>75</v>
@@ -81878,7 +81881,7 @@
     </row>
     <row r="729">
       <c r="A729" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B729" t="s" s="2">
         <v>1162</v>
@@ -81985,7 +81988,7 @@
     </row>
     <row r="730">
       <c r="A730" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B730" t="s" s="2">
         <v>1167</v>
@@ -82088,7 +82091,7 @@
     </row>
     <row r="731">
       <c r="A731" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B731" t="s" s="2">
         <v>1171</v>
@@ -82120,7 +82123,7 @@
         <v>364</v>
       </c>
       <c r="M731" t="s" s="2">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="N731" t="s" s="2">
         <v>1173</v>
@@ -82195,7 +82198,7 @@
     </row>
     <row r="732">
       <c r="A732" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B732" t="s" s="2">
         <v>1176</v>
@@ -82224,10 +82227,10 @@
         <v>85</v>
       </c>
       <c r="L732" t="s" s="2">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="M732" t="s" s="2">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="N732" t="s" s="2">
         <v>1180</v>
@@ -82302,13 +82305,13 @@
     </row>
     <row r="733">
       <c r="A733" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B733" t="s" s="2">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="C733" t="s" s="2">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="D733" s="2"/>
       <c r="E733" t="s" s="2">
@@ -82405,13 +82408,13 @@
     </row>
     <row r="734">
       <c r="A734" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B734" t="s" s="2">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="C734" t="s" s="2">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="D734" s="2"/>
       <c r="E734" t="s" s="2">
@@ -82510,16 +82513,16 @@
     </row>
     <row r="735">
       <c r="A735" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B735" t="s" s="2">
+        <v>1311</v>
+      </c>
+      <c r="C735" t="s" s="2">
         <v>1310</v>
       </c>
-      <c r="C735" t="s" s="2">
-        <v>1309</v>
-      </c>
       <c r="D735" t="s" s="2">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="E735" t="s" s="2">
         <v>75</v>
@@ -82541,13 +82544,13 @@
         <v>75</v>
       </c>
       <c r="L735" t="s" s="2">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="M735" t="s" s="2">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="N735" t="s" s="2">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="O735" s="2"/>
       <c r="P735" s="2"/>
@@ -82615,13 +82618,13 @@
     </row>
     <row r="736">
       <c r="A736" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B736" t="s" s="2">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="C736" t="s" s="2">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="D736" s="2"/>
       <c r="E736" t="s" s="2">
@@ -82718,13 +82721,13 @@
     </row>
     <row r="737">
       <c r="A737" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B737" t="s" s="2">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="C737" t="s" s="2">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="D737" s="2"/>
       <c r="E737" t="s" s="2">
@@ -82821,13 +82824,13 @@
     </row>
     <row r="738">
       <c r="A738" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B738" t="s" s="2">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="C738" t="s" s="2">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="D738" s="2"/>
       <c r="E738" t="s" s="2">
@@ -82867,7 +82870,7 @@
       </c>
       <c r="R738" s="2"/>
       <c r="S738" t="s" s="2">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="T738" t="s" s="2">
         <v>75</v>
@@ -82926,13 +82929,13 @@
     </row>
     <row r="739">
       <c r="A739" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B739" t="s" s="2">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="C739" t="s" s="2">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="D739" s="2"/>
       <c r="E739" t="s" s="2">
@@ -82955,7 +82958,7 @@
         <v>75</v>
       </c>
       <c r="L739" t="s" s="2">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="M739" t="s" s="2">
         <v>1011</v>
@@ -83029,13 +83032,13 @@
     </row>
     <row r="740">
       <c r="A740" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B740" t="s" s="2">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="C740" t="s" s="2">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="D740" s="2"/>
       <c r="E740" t="s" s="2">
@@ -83134,13 +83137,13 @@
     </row>
     <row r="741">
       <c r="A741" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B741" t="s" s="2">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="C741" t="s" s="2">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="D741" s="2"/>
       <c r="E741" t="s" s="2">
@@ -83239,13 +83242,13 @@
     </row>
     <row r="742">
       <c r="A742" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B742" t="s" s="2">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="C742" t="s" s="2">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="D742" s="2"/>
       <c r="E742" t="s" s="2">
@@ -83344,13 +83347,13 @@
     </row>
     <row r="743">
       <c r="A743" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B743" t="s" s="2">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="C743" t="s" s="2">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="D743" s="2"/>
       <c r="E743" t="s" s="2">
@@ -83449,7 +83452,7 @@
     </row>
     <row r="744">
       <c r="A744" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B744" t="s" s="2">
         <v>1183</v>
@@ -83556,7 +83559,7 @@
     </row>
     <row r="745">
       <c r="A745" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B745" t="s" s="2">
         <v>1190</v>
@@ -83588,7 +83591,7 @@
         <v>1191</v>
       </c>
       <c r="M745" t="s" s="2">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="N745" t="s" s="2">
         <v>1193</v>
@@ -83659,7 +83662,7 @@
     </row>
     <row r="746">
       <c r="A746" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B746" t="s" s="2">
         <v>1194</v>
@@ -83691,7 +83694,7 @@
         <v>258</v>
       </c>
       <c r="M746" t="s" s="2">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="N746" t="s" s="2">
         <v>1196</v>
@@ -83764,7 +83767,7 @@
     </row>
     <row r="747">
       <c r="A747" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B747" t="s" s="2">
         <v>1199</v>
@@ -83867,7 +83870,7 @@
     </row>
     <row r="748">
       <c r="A748" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B748" t="s" s="2">
         <v>1200</v>
@@ -83972,7 +83975,7 @@
     </row>
     <row r="749">
       <c r="A749" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B749" t="s" s="2">
         <v>1201</v>
@@ -84079,7 +84082,7 @@
     </row>
     <row r="750">
       <c r="A750" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B750" t="s" s="2">
         <v>1202</v>
@@ -84186,7 +84189,7 @@
     </row>
     <row r="751">
       <c r="A751" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B751" t="s" s="2">
         <v>1209</v>
@@ -84295,7 +84298,7 @@
     </row>
     <row r="752">
       <c r="A752" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B752" t="s" s="2">
         <v>1216</v>
@@ -84400,7 +84403,7 @@
     </row>
     <row r="753">
       <c r="A753" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B753" t="s" s="2">
         <v>1220</v>
@@ -84429,10 +84432,10 @@
         <v>75</v>
       </c>
       <c r="L753" t="s" s="2">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="M753" t="s" s="2">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="N753" t="s" s="2">
         <v>1223</v>
@@ -84503,7 +84506,7 @@
     </row>
     <row r="754">
       <c r="A754" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B754" t="s" s="2">
         <v>1224</v>

--- a/nr-securitylabel-slicing-123/ig/all-profiles.xlsx
+++ b/nr-securitylabel-slicing-123/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T14:05:46+00:00</t>
+    <t>2026-08-06T14:06:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -947,7 +947,7 @@
 </t>
   </si>
   <si>
-    <t>Slice sur securityLabel pour distinguer le niveau de confidentialité (NRV) du statut de visibilité complémentaire (TRE A07) : chaque slice est discriminée par son required binding sur un ValueSet fermé (v3-ConfidentialityClassification pour confidentiality, JDV_J110-StatutVisibiliteDocument-CISIS pour visibilityStatus)</t>
+    <t>Slice sur securityLabel pour distinguer le niveau de confidentialité (U, L, M, N, R, V) du statut de visibilité (MASQUE_PS, INVISIBLE_PATIENT, etc...) : chaque slice est discriminée par son required binding sur un ValueSet fermé (v3-ConfidentialityClassification pour confidentiality, JDV_J110-StatutVisibiliteDocument-CISIS pour visibilityStatus)</t>
   </si>
   <si>
     <t>DocumentReference.securityLabel:confidentiality</t>
@@ -3920,7 +3920,7 @@
     <t>Commentaire associé au document.</t>
   </si>
   <si>
-    <t>Statut de visibilité complémentaire du document (motifs de masquage patient, représentants légaux, professionnels).</t>
+    <t>Slice sur securityLabel pour distinguer le niveau de confidentialité (NRV) du statut de visibilité complémentaire (TRE A07) : chaque slice est discriminée par son required binding sur un ValueSet fermé (v3-ConfidentialityClassification pour confidentiality, JDV_J110-StatutVisibiliteDocument-CISIS pour visibilityStatus)</t>
   </si>
   <si>
     <t>Document contenu.</t>
@@ -5845,7 +5845,7 @@
     <col min="27" max="27" width="102.93359375" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="249.46875" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="255.0" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.7578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="37.78125" customWidth="true" bestFit="true" hidden="true"/>
@@ -74959,7 +74959,7 @@
         <v>292</v>
       </c>
       <c r="AD662" t="s" s="2">
-        <v>293</v>
+        <v>1252</v>
       </c>
       <c r="AE662" t="s" s="2">
         <v>75</v>
@@ -75126,7 +75126,7 @@
         <v>220</v>
       </c>
       <c r="M664" t="s" s="2">
-        <v>1252</v>
+        <v>300</v>
       </c>
       <c r="N664" t="s" s="2">
         <v>289</v>

--- a/nr-securitylabel-slicing-123/ig/all-profiles.xlsx
+++ b/nr-securitylabel-slicing-123/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25067" uniqueCount="1334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25067" uniqueCount="1333">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T14:06:47+00:00</t>
+    <t>2026-08-06T14:07:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3918,9 +3918,6 @@
   </si>
   <si>
     <t>Commentaire associé au document.</t>
-  </si>
-  <si>
-    <t>Slice sur securityLabel pour distinguer le niveau de confidentialité (NRV) du statut de visibilité complémentaire (TRE A07) : chaque slice est discriminée par son required binding sur un ValueSet fermé (v3-ConfidentialityClassification pour confidentiality, JDV_J110-StatutVisibiliteDocument-CISIS pour visibilityStatus)</t>
   </si>
   <si>
     <t>Document contenu.</t>
@@ -5657,7 +5654,7 @@
         <v>2</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="174">
@@ -5665,7 +5662,7 @@
         <v>4</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="175">
@@ -5681,7 +5678,7 @@
         <v>8</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="177">
@@ -5689,7 +5686,7 @@
         <v>10</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="178">
@@ -5743,7 +5740,7 @@
         <v>23</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="185">
@@ -5787,7 +5784,7 @@
         <v>33</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="191">
@@ -74959,7 +74956,7 @@
         <v>292</v>
       </c>
       <c r="AD662" t="s" s="2">
-        <v>1252</v>
+        <v>293</v>
       </c>
       <c r="AE662" t="s" s="2">
         <v>75</v>
@@ -75231,7 +75228,7 @@
         <v>258</v>
       </c>
       <c r="M665" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="N665" t="s" s="2">
         <v>304</v>
@@ -76170,7 +76167,7 @@
         <v>329</v>
       </c>
       <c r="M674" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="N674" t="s" s="2">
         <v>331</v>
@@ -76277,7 +76274,7 @@
         <v>336</v>
       </c>
       <c r="M675" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="N675" t="s" s="2">
         <v>338</v>
@@ -76703,7 +76700,7 @@
         <v>364</v>
       </c>
       <c r="M679" t="s" s="2">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="N679" t="s" s="2">
         <v>366</v>
@@ -77706,7 +77703,7 @@
         <v>75</v>
       </c>
       <c r="AK688" t="s" s="2">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="689">
@@ -77811,7 +77808,7 @@
         <v>75</v>
       </c>
       <c r="AK689" t="s" s="2">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="690">
@@ -78024,7 +78021,7 @@
     </row>
     <row r="692">
       <c r="A692" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B692" t="s" s="2">
         <v>1103</v>
@@ -78127,7 +78124,7 @@
     </row>
     <row r="693">
       <c r="A693" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B693" t="s" s="2">
         <v>1106</v>
@@ -78232,7 +78229,7 @@
     </row>
     <row r="694">
       <c r="A694" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B694" t="s" s="2">
         <v>1107</v>
@@ -78335,7 +78332,7 @@
     </row>
     <row r="695">
       <c r="A695" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B695" t="s" s="2">
         <v>1108</v>
@@ -78438,7 +78435,7 @@
     </row>
     <row r="696">
       <c r="A696" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B696" t="s" s="2">
         <v>1109</v>
@@ -78543,7 +78540,7 @@
     </row>
     <row r="697">
       <c r="A697" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B697" t="s" s="2">
         <v>1110</v>
@@ -78648,7 +78645,7 @@
     </row>
     <row r="698">
       <c r="A698" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B698" t="s" s="2">
         <v>1111</v>
@@ -78753,7 +78750,7 @@
     </row>
     <row r="699">
       <c r="A699" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B699" t="s" s="2">
         <v>1112</v>
@@ -78858,7 +78855,7 @@
     </row>
     <row r="700">
       <c r="A700" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B700" t="s" s="2">
         <v>1113</v>
@@ -78963,7 +78960,7 @@
     </row>
     <row r="701">
       <c r="A701" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B701" t="s" s="2">
         <v>1114</v>
@@ -79068,7 +79065,7 @@
     </row>
     <row r="702">
       <c r="A702" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B702" t="s" s="2">
         <v>1115</v>
@@ -79173,7 +79170,7 @@
     </row>
     <row r="703">
       <c r="A703" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B703" t="s" s="2">
         <v>1116</v>
@@ -79278,7 +79275,7 @@
     </row>
     <row r="704">
       <c r="A704" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B704" t="s" s="2">
         <v>1117</v>
@@ -79383,7 +79380,7 @@
     </row>
     <row r="705">
       <c r="A705" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B705" t="s" s="2">
         <v>1118</v>
@@ -79488,7 +79485,7 @@
     </row>
     <row r="706">
       <c r="A706" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B706" t="s" s="2">
         <v>1119</v>
@@ -79520,7 +79517,7 @@
         <v>176</v>
       </c>
       <c r="M706" t="s" s="2">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="N706" t="s" s="2">
         <v>178</v>
@@ -79593,7 +79590,7 @@
     </row>
     <row r="707">
       <c r="A707" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B707" t="s" s="2">
         <v>1121</v>
@@ -79607,7 +79604,7 @@
       </c>
       <c r="F707" s="2"/>
       <c r="G707" t="s" s="2">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="H707" t="s" s="2">
         <v>77</v>
@@ -79694,7 +79691,7 @@
     </row>
     <row r="708">
       <c r="A708" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B708" t="s" s="2">
         <v>1122</v>
@@ -79728,7 +79725,7 @@
         <v>1124</v>
       </c>
       <c r="M708" t="s" s="2">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="N708" t="s" s="2">
         <v>1126</v>
@@ -79794,18 +79791,18 @@
         <v>190</v>
       </c>
       <c r="AK708" t="s" s="2">
-        <v>1267</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B709" t="s" s="2">
+        <v>1267</v>
+      </c>
+      <c r="C709" t="s" s="2">
         <v>1268</v>
-      </c>
-      <c r="C709" t="s" s="2">
-        <v>1269</v>
       </c>
       <c r="D709" s="2"/>
       <c r="E709" t="s" s="2">
@@ -79902,13 +79899,13 @@
     </row>
     <row r="710">
       <c r="A710" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B710" t="s" s="2">
+        <v>1269</v>
+      </c>
+      <c r="C710" t="s" s="2">
         <v>1270</v>
-      </c>
-      <c r="C710" t="s" s="2">
-        <v>1271</v>
       </c>
       <c r="D710" s="2"/>
       <c r="E710" t="s" s="2">
@@ -80005,13 +80002,13 @@
     </row>
     <row r="711">
       <c r="A711" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B711" t="s" s="2">
+        <v>1271</v>
+      </c>
+      <c r="C711" t="s" s="2">
         <v>1272</v>
-      </c>
-      <c r="C711" t="s" s="2">
-        <v>1273</v>
       </c>
       <c r="D711" s="2"/>
       <c r="E711" t="s" s="2">
@@ -80051,7 +80048,7 @@
       </c>
       <c r="R711" s="2"/>
       <c r="S711" t="s" s="2">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="T711" t="s" s="2">
         <v>75</v>
@@ -80110,13 +80107,13 @@
     </row>
     <row r="712">
       <c r="A712" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B712" t="s" s="2">
+        <v>1274</v>
+      </c>
+      <c r="C712" t="s" s="2">
         <v>1275</v>
-      </c>
-      <c r="C712" t="s" s="2">
-        <v>1276</v>
       </c>
       <c r="D712" s="2"/>
       <c r="E712" t="s" s="2">
@@ -80176,7 +80173,7 @@
       </c>
       <c r="Z712" s="2"/>
       <c r="AA712" t="s" s="2">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="AB712" t="s" s="2">
         <v>75</v>
@@ -80211,16 +80208,16 @@
     </row>
     <row r="713">
       <c r="A713" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B713" t="s" s="2">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="C713" t="s" s="2">
         <v>1121</v>
       </c>
       <c r="D713" t="s" s="2">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="E713" t="s" s="2">
         <v>75</v>
@@ -80242,13 +80239,13 @@
         <v>75</v>
       </c>
       <c r="L713" t="s" s="2">
+        <v>1279</v>
+      </c>
+      <c r="M713" t="s" s="2">
         <v>1280</v>
       </c>
-      <c r="M713" t="s" s="2">
+      <c r="N713" t="s" s="2">
         <v>1281</v>
-      </c>
-      <c r="N713" t="s" s="2">
-        <v>1282</v>
       </c>
       <c r="O713" s="2"/>
       <c r="P713" s="2"/>
@@ -80316,16 +80313,16 @@
     </row>
     <row r="714">
       <c r="A714" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B714" t="s" s="2">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="C714" t="s" s="2">
         <v>1121</v>
       </c>
       <c r="D714" t="s" s="2">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="E714" t="s" s="2">
         <v>75</v>
@@ -80347,13 +80344,13 @@
         <v>75</v>
       </c>
       <c r="L714" t="s" s="2">
+        <v>1284</v>
+      </c>
+      <c r="M714" t="s" s="2">
         <v>1285</v>
       </c>
-      <c r="M714" t="s" s="2">
+      <c r="N714" t="s" s="2">
         <v>1286</v>
-      </c>
-      <c r="N714" t="s" s="2">
-        <v>1287</v>
       </c>
       <c r="O714" s="2"/>
       <c r="P714" s="2"/>
@@ -80421,10 +80418,10 @@
     </row>
     <row r="715">
       <c r="A715" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B715" t="s" s="2">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="C715" t="s" s="2">
         <v>1121</v>
@@ -80455,7 +80452,7 @@
         <v>187</v>
       </c>
       <c r="M715" t="s" s="2">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="N715" t="s" s="2">
         <v>189</v>
@@ -80526,16 +80523,16 @@
     </row>
     <row r="716">
       <c r="A716" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B716" t="s" s="2">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="C716" t="s" s="2">
         <v>1121</v>
       </c>
       <c r="D716" t="s" s="2">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="E716" t="s" s="2">
         <v>75</v>
@@ -80557,10 +80554,10 @@
         <v>75</v>
       </c>
       <c r="L716" t="s" s="2">
+        <v>1291</v>
+      </c>
+      <c r="M716" t="s" s="2">
         <v>1292</v>
-      </c>
-      <c r="M716" t="s" s="2">
-        <v>1293</v>
       </c>
       <c r="N716" t="s" s="2">
         <v>998</v>
@@ -80631,13 +80628,13 @@
     </row>
     <row r="717">
       <c r="A717" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B717" t="s" s="2">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="C717" t="s" s="2">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="D717" s="2"/>
       <c r="E717" t="s" s="2">
@@ -80734,13 +80731,13 @@
     </row>
     <row r="718">
       <c r="A718" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B718" t="s" s="2">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C718" t="s" s="2">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="D718" s="2"/>
       <c r="E718" t="s" s="2">
@@ -80837,13 +80834,13 @@
     </row>
     <row r="719">
       <c r="A719" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B719" t="s" s="2">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="C719" t="s" s="2">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="D719" s="2"/>
       <c r="E719" t="s" s="2">
@@ -80942,13 +80939,13 @@
     </row>
     <row r="720">
       <c r="A720" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B720" t="s" s="2">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="C720" t="s" s="2">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="D720" s="2"/>
       <c r="E720" t="s" s="2">
@@ -81045,7 +81042,7 @@
     </row>
     <row r="721">
       <c r="A721" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B721" t="s" s="2">
         <v>1127</v>
@@ -81148,7 +81145,7 @@
     </row>
     <row r="722">
       <c r="A722" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B722" t="s" s="2">
         <v>1128</v>
@@ -81249,7 +81246,7 @@
     </row>
     <row r="723">
       <c r="A723" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B723" t="s" s="2">
         <v>1131</v>
@@ -81280,10 +81277,10 @@
         <v>75</v>
       </c>
       <c r="L723" t="s" s="2">
+        <v>1297</v>
+      </c>
+      <c r="M723" t="s" s="2">
         <v>1298</v>
-      </c>
-      <c r="M723" t="s" s="2">
-        <v>1299</v>
       </c>
       <c r="N723" t="s" s="2">
         <v>1130</v>
@@ -81354,7 +81351,7 @@
     </row>
     <row r="724">
       <c r="A724" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B724" t="s" s="2">
         <v>1134</v>
@@ -81388,7 +81385,7 @@
         <v>206</v>
       </c>
       <c r="M724" t="s" s="2">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="N724" t="s" s="2">
         <v>1130</v>
@@ -81459,7 +81456,7 @@
     </row>
     <row r="725">
       <c r="A725" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B725" t="s" s="2">
         <v>1136</v>
@@ -81491,7 +81488,7 @@
         <v>159</v>
       </c>
       <c r="M725" t="s" s="2">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="N725" t="s" s="2">
         <v>1138</v>
@@ -81564,7 +81561,7 @@
     </row>
     <row r="726">
       <c r="A726" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B726" t="s" s="2">
         <v>1142</v>
@@ -81596,7 +81593,7 @@
         <v>159</v>
       </c>
       <c r="M726" t="s" s="2">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="N726" t="s" s="2">
         <v>1144</v>
@@ -81671,7 +81668,7 @@
     </row>
     <row r="727">
       <c r="A727" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B727" t="s" s="2">
         <v>1150</v>
@@ -81703,7 +81700,7 @@
         <v>98</v>
       </c>
       <c r="M727" t="s" s="2">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="N727" t="s" s="2">
         <v>1152</v>
@@ -81776,7 +81773,7 @@
     </row>
     <row r="728">
       <c r="A728" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B728" t="s" s="2">
         <v>1155</v>
@@ -81808,7 +81805,7 @@
         <v>220</v>
       </c>
       <c r="M728" t="s" s="2">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="N728" t="s" s="2">
         <v>1157</v>
@@ -81827,7 +81824,7 @@
         <v>75</v>
       </c>
       <c r="T728" t="s" s="2">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="U728" t="s" s="2">
         <v>75</v>
@@ -81881,7 +81878,7 @@
     </row>
     <row r="729">
       <c r="A729" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B729" t="s" s="2">
         <v>1162</v>
@@ -81988,7 +81985,7 @@
     </row>
     <row r="730">
       <c r="A730" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B730" t="s" s="2">
         <v>1167</v>
@@ -82091,7 +82088,7 @@
     </row>
     <row r="731">
       <c r="A731" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B731" t="s" s="2">
         <v>1171</v>
@@ -82123,7 +82120,7 @@
         <v>364</v>
       </c>
       <c r="M731" t="s" s="2">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="N731" t="s" s="2">
         <v>1173</v>
@@ -82198,7 +82195,7 @@
     </row>
     <row r="732">
       <c r="A732" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B732" t="s" s="2">
         <v>1176</v>
@@ -82227,10 +82224,10 @@
         <v>85</v>
       </c>
       <c r="L732" t="s" s="2">
+        <v>1306</v>
+      </c>
+      <c r="M732" t="s" s="2">
         <v>1307</v>
-      </c>
-      <c r="M732" t="s" s="2">
-        <v>1308</v>
       </c>
       <c r="N732" t="s" s="2">
         <v>1180</v>
@@ -82305,13 +82302,13 @@
     </row>
     <row r="733">
       <c r="A733" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B733" t="s" s="2">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="C733" t="s" s="2">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="D733" s="2"/>
       <c r="E733" t="s" s="2">
@@ -82408,13 +82405,13 @@
     </row>
     <row r="734">
       <c r="A734" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B734" t="s" s="2">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C734" t="s" s="2">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="D734" s="2"/>
       <c r="E734" t="s" s="2">
@@ -82513,16 +82510,16 @@
     </row>
     <row r="735">
       <c r="A735" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B735" t="s" s="2">
+        <v>1310</v>
+      </c>
+      <c r="C735" t="s" s="2">
+        <v>1309</v>
+      </c>
+      <c r="D735" t="s" s="2">
         <v>1311</v>
-      </c>
-      <c r="C735" t="s" s="2">
-        <v>1310</v>
-      </c>
-      <c r="D735" t="s" s="2">
-        <v>1312</v>
       </c>
       <c r="E735" t="s" s="2">
         <v>75</v>
@@ -82544,13 +82541,13 @@
         <v>75</v>
       </c>
       <c r="L735" t="s" s="2">
+        <v>1312</v>
+      </c>
+      <c r="M735" t="s" s="2">
         <v>1313</v>
       </c>
-      <c r="M735" t="s" s="2">
+      <c r="N735" t="s" s="2">
         <v>1314</v>
-      </c>
-      <c r="N735" t="s" s="2">
-        <v>1315</v>
       </c>
       <c r="O735" s="2"/>
       <c r="P735" s="2"/>
@@ -82618,13 +82615,13 @@
     </row>
     <row r="736">
       <c r="A736" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B736" t="s" s="2">
+        <v>1315</v>
+      </c>
+      <c r="C736" t="s" s="2">
         <v>1316</v>
-      </c>
-      <c r="C736" t="s" s="2">
-        <v>1317</v>
       </c>
       <c r="D736" s="2"/>
       <c r="E736" t="s" s="2">
@@ -82721,13 +82718,13 @@
     </row>
     <row r="737">
       <c r="A737" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B737" t="s" s="2">
+        <v>1317</v>
+      </c>
+      <c r="C737" t="s" s="2">
         <v>1318</v>
-      </c>
-      <c r="C737" t="s" s="2">
-        <v>1319</v>
       </c>
       <c r="D737" s="2"/>
       <c r="E737" t="s" s="2">
@@ -82824,13 +82821,13 @@
     </row>
     <row r="738">
       <c r="A738" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B738" t="s" s="2">
+        <v>1319</v>
+      </c>
+      <c r="C738" t="s" s="2">
         <v>1320</v>
-      </c>
-      <c r="C738" t="s" s="2">
-        <v>1321</v>
       </c>
       <c r="D738" s="2"/>
       <c r="E738" t="s" s="2">
@@ -82870,7 +82867,7 @@
       </c>
       <c r="R738" s="2"/>
       <c r="S738" t="s" s="2">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="T738" t="s" s="2">
         <v>75</v>
@@ -82929,13 +82926,13 @@
     </row>
     <row r="739">
       <c r="A739" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B739" t="s" s="2">
+        <v>1322</v>
+      </c>
+      <c r="C739" t="s" s="2">
         <v>1323</v>
-      </c>
-      <c r="C739" t="s" s="2">
-        <v>1324</v>
       </c>
       <c r="D739" s="2"/>
       <c r="E739" t="s" s="2">
@@ -82958,7 +82955,7 @@
         <v>75</v>
       </c>
       <c r="L739" t="s" s="2">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="M739" t="s" s="2">
         <v>1011</v>
@@ -83032,13 +83029,13 @@
     </row>
     <row r="740">
       <c r="A740" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B740" t="s" s="2">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="C740" t="s" s="2">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="D740" s="2"/>
       <c r="E740" t="s" s="2">
@@ -83137,13 +83134,13 @@
     </row>
     <row r="741">
       <c r="A741" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B741" t="s" s="2">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="C741" t="s" s="2">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="D741" s="2"/>
       <c r="E741" t="s" s="2">
@@ -83242,13 +83239,13 @@
     </row>
     <row r="742">
       <c r="A742" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B742" t="s" s="2">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="C742" t="s" s="2">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="D742" s="2"/>
       <c r="E742" t="s" s="2">
@@ -83347,13 +83344,13 @@
     </row>
     <row r="743">
       <c r="A743" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B743" t="s" s="2">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="C743" t="s" s="2">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="D743" s="2"/>
       <c r="E743" t="s" s="2">
@@ -83452,7 +83449,7 @@
     </row>
     <row r="744">
       <c r="A744" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B744" t="s" s="2">
         <v>1183</v>
@@ -83559,7 +83556,7 @@
     </row>
     <row r="745">
       <c r="A745" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B745" t="s" s="2">
         <v>1190</v>
@@ -83591,7 +83588,7 @@
         <v>1191</v>
       </c>
       <c r="M745" t="s" s="2">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="N745" t="s" s="2">
         <v>1193</v>
@@ -83662,7 +83659,7 @@
     </row>
     <row r="746">
       <c r="A746" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B746" t="s" s="2">
         <v>1194</v>
@@ -83694,7 +83691,7 @@
         <v>258</v>
       </c>
       <c r="M746" t="s" s="2">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="N746" t="s" s="2">
         <v>1196</v>
@@ -83767,7 +83764,7 @@
     </row>
     <row r="747">
       <c r="A747" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B747" t="s" s="2">
         <v>1199</v>
@@ -83870,7 +83867,7 @@
     </row>
     <row r="748">
       <c r="A748" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B748" t="s" s="2">
         <v>1200</v>
@@ -83975,7 +83972,7 @@
     </row>
     <row r="749">
       <c r="A749" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B749" t="s" s="2">
         <v>1201</v>
@@ -84082,7 +84079,7 @@
     </row>
     <row r="750">
       <c r="A750" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B750" t="s" s="2">
         <v>1202</v>
@@ -84189,7 +84186,7 @@
     </row>
     <row r="751">
       <c r="A751" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B751" t="s" s="2">
         <v>1209</v>
@@ -84298,7 +84295,7 @@
     </row>
     <row r="752">
       <c r="A752" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B752" t="s" s="2">
         <v>1216</v>
@@ -84403,7 +84400,7 @@
     </row>
     <row r="753">
       <c r="A753" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B753" t="s" s="2">
         <v>1220</v>
@@ -84432,10 +84429,10 @@
         <v>75</v>
       </c>
       <c r="L753" t="s" s="2">
+        <v>1331</v>
+      </c>
+      <c r="M753" t="s" s="2">
         <v>1332</v>
-      </c>
-      <c r="M753" t="s" s="2">
-        <v>1333</v>
       </c>
       <c r="N753" t="s" s="2">
         <v>1223</v>
@@ -84506,7 +84503,7 @@
     </row>
     <row r="754">
       <c r="A754" t="s" s="2">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B754" t="s" s="2">
         <v>1224</v>
